--- a/data/Data trimestral 1950 a 2023.xlsx
+++ b/data/Data trimestral 1950 a 2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianabarrena/Library/CloudStorage/GoogleDrive-marianabarrena@derecho.uba.ar/Mi unidad/UCA Sincronizado/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0045864C-B3C3-9D4E-96F9-9D250478139D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42974DFD-97E4-8243-8811-C240BDCCCFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1340" windowWidth="38400" windowHeight="21100" xr2:uid="{081104FB-1F73-C945-9C9A-B52E522B90FE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{081104FB-1F73-C945-9C9A-B52E522B90FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -248,9 +248,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -288,7 +288,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -394,7 +394,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -536,7 +536,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -614,7 +614,9 @@
       <c r="F2" s="17">
         <v>141630</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5">
+        <v>10.92034854649366</v>
+      </c>
       <c r="H2" s="7">
         <v>2.16</v>
       </c>
@@ -643,7 +645,9 @@
       <c r="F3" s="17">
         <v>139320</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="5">
+        <v>11.19826160830563</v>
+      </c>
       <c r="H3" s="7">
         <v>2.6633333333333331</v>
       </c>
@@ -672,7 +676,9 @@
       <c r="F4" s="17">
         <v>144669</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="5">
+        <v>12.162783411064799</v>
+      </c>
       <c r="H4" s="7">
         <v>2.5366666666666666</v>
       </c>
@@ -701,7 +707,9 @@
       <c r="F5" s="17">
         <v>142804</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="5">
+        <v>13.24174000398183</v>
+      </c>
       <c r="H5" s="7">
         <v>2.4233333333333333</v>
       </c>
@@ -730,7 +738,9 @@
       <c r="F6" s="17">
         <v>146731</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="5">
+        <v>14.45147921422215</v>
+      </c>
       <c r="H6" s="7">
         <v>3.0266666666666668</v>
       </c>
@@ -759,7 +769,9 @@
       <c r="F7" s="17">
         <v>148515</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="5">
+        <v>15.350609708319681</v>
+      </c>
       <c r="H7" s="7">
         <v>3.0766666666666667</v>
       </c>
@@ -788,7 +800,9 @@
       <c r="F8" s="17">
         <v>147595</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="5">
+        <v>15.30156622682345</v>
+      </c>
       <c r="H8" s="7">
         <v>2.72</v>
       </c>
@@ -817,7 +831,9 @@
       <c r="F9" s="17">
         <v>146949</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="5">
+        <v>14.680348794537879</v>
+      </c>
       <c r="H9" s="7">
         <v>2.74</v>
       </c>
@@ -846,7 +862,9 @@
       <c r="F10" s="17">
         <v>147305</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="5">
+        <v>14.713044448868709</v>
+      </c>
       <c r="H10" s="7">
         <v>2.7733333333333334</v>
       </c>
@@ -875,7 +893,9 @@
       <c r="F11" s="17">
         <v>142608</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="5">
+        <v>14.30434876973346</v>
+      </c>
       <c r="H11" s="7">
         <v>2.8366666666666664</v>
       </c>
@@ -904,7 +924,9 @@
       <c r="F12" s="17">
         <v>135474</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="5">
+        <v>13.912000917763629</v>
+      </c>
       <c r="H12" s="7">
         <v>2.9599999999999995</v>
       </c>
@@ -933,7 +955,9 @@
       <c r="F13" s="17">
         <v>136685</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="5">
+        <v>13.666783510282491</v>
+      </c>
       <c r="H13" s="7">
         <v>2.7233333333333332</v>
       </c>
@@ -962,7 +986,9 @@
       <c r="F14" s="17">
         <v>140357</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="5">
+        <v>13.5850443744554</v>
+      </c>
       <c r="H14" s="7">
         <v>2.7100000000000004</v>
       </c>
@@ -991,7 +1017,9 @@
       <c r="F15" s="17">
         <v>146396</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="5">
+        <v>13.55234872012462</v>
+      </c>
       <c r="H15" s="7">
         <v>2.75</v>
       </c>
@@ -1020,7 +1048,9 @@
       <c r="F16" s="17">
         <v>149849</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="5">
+        <v>13.60139220162085</v>
+      </c>
       <c r="H16" s="7">
         <v>2.39</v>
       </c>
@@ -1049,7 +1079,9 @@
       <c r="F17" s="17">
         <v>152698</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="5">
+        <v>13.53600089295921</v>
+      </c>
       <c r="H17" s="7">
         <v>2.6066666666666669</v>
       </c>
@@ -1078,7 +1110,9 @@
       <c r="F18" s="17">
         <v>151482</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="G18" s="5">
+        <v>13.585044374455441</v>
+      </c>
       <c r="H18" s="7">
         <v>3.0066666666666673</v>
       </c>
@@ -1107,7 +1141,9 @@
       <c r="F19" s="17">
         <v>145721</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="5">
+        <v>13.83026178193658</v>
+      </c>
       <c r="H19" s="7">
         <v>3.52</v>
       </c>
@@ -1136,7 +1172,9 @@
       <c r="F20" s="17">
         <v>154371</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="5">
+        <v>14.05913136225232</v>
+      </c>
       <c r="H20" s="7">
         <v>3.0700000000000003</v>
       </c>
@@ -1165,7 +1203,9 @@
       <c r="F21" s="17">
         <v>161721</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="5">
+        <v>13.928348744929041</v>
+      </c>
       <c r="H21" s="7">
         <v>2.56</v>
       </c>
@@ -1194,7 +1234,9 @@
       <c r="F22" s="17">
         <v>163812</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="5">
+        <v>13.862957436267401</v>
+      </c>
       <c r="H22" s="7">
         <v>2.5766666666666667</v>
       </c>
@@ -1223,7 +1265,9 @@
       <c r="F23" s="17">
         <v>164488</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="5">
+        <v>13.74852264610954</v>
+      </c>
       <c r="H23" s="7">
         <v>2.3666666666666667</v>
       </c>
@@ -1252,7 +1296,9 @@
       <c r="F24" s="17">
         <v>162475</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="5">
+        <v>13.74852264610954</v>
+      </c>
       <c r="H24" s="7">
         <v>2.1433333333333331</v>
       </c>
@@ -1281,7 +1327,9 @@
       <c r="F25" s="17">
         <v>164896</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="5">
+        <v>13.89565309059822</v>
+      </c>
       <c r="H25" s="7">
         <v>2.0833333333333335</v>
       </c>
@@ -1310,7 +1358,9 @@
       <c r="F26" s="17">
         <v>171503</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="5">
+        <v>14.075479189417729</v>
+      </c>
       <c r="H26" s="7">
         <v>2.273333333333333</v>
       </c>
@@ -1339,7 +1389,9 @@
       <c r="F27" s="17">
         <v>171220</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="5">
+        <v>14.12452267091396</v>
+      </c>
       <c r="H27" s="7">
         <v>2.8266666666666667</v>
       </c>
@@ -1368,7 +1420,9 @@
       <c r="F28" s="17">
         <v>171068</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="5">
+        <v>14.091827016583141</v>
+      </c>
       <c r="H28" s="7">
         <v>2.2900000000000005</v>
       </c>
@@ -1397,7 +1451,9 @@
       <c r="F29" s="17">
         <v>160707</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="5">
+        <v>14.222609633906419</v>
+      </c>
       <c r="H29" s="7">
         <v>2.2033333333333331</v>
       </c>
@@ -14674,5 +14730,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>